--- a/sample_data/output/excel/07_NICE_소득_시군구별.xlsx
+++ b/sample_data/output/excel/07_NICE_소득_시군구별.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2179</v>
+        <v>787</v>
       </c>
       <c r="E2" t="n">
-        <v>2558.6</v>
+        <v>2502.5</v>
       </c>
       <c r="F2" t="n">
-        <v>2266.8</v>
+        <v>2333</v>
       </c>
       <c r="G2" t="n">
-        <v>4719466</v>
+        <v>1706661</v>
       </c>
     </row>
     <row r="3">
@@ -499,16 +499,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3231</v>
+        <v>1546</v>
       </c>
       <c r="E3" t="n">
-        <v>3908.416666666667</v>
+        <v>5036.666666666667</v>
       </c>
       <c r="F3" t="n">
-        <v>3219.5</v>
+        <v>3894</v>
       </c>
       <c r="G3" t="n">
-        <v>14038894</v>
+        <v>9149659</v>
       </c>
     </row>
     <row r="4">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3631</v>
+        <v>196</v>
       </c>
       <c r="E4" t="n">
-        <v>5303.166666666667</v>
+        <v>6344</v>
       </c>
       <c r="F4" t="n">
-        <v>4427.5</v>
+        <v>4697</v>
       </c>
       <c r="G4" t="n">
-        <v>20395924</v>
+        <v>1243424</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4315</v>
+        <v>313</v>
       </c>
       <c r="E5" t="n">
-        <v>4379</v>
+        <v>7051</v>
       </c>
       <c r="F5" t="n">
-        <v>3603.142857142857</v>
+        <v>5851</v>
       </c>
       <c r="G5" t="n">
-        <v>20623903</v>
+        <v>2206963</v>
       </c>
     </row>
     <row r="6">
@@ -586,16 +586,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3928</v>
+        <v>1003</v>
       </c>
       <c r="E6" t="n">
-        <v>3615.690476190476</v>
+        <v>6040.75</v>
       </c>
       <c r="F6" t="n">
-        <v>3234.928571428572</v>
+        <v>5528</v>
       </c>
       <c r="G6" t="n">
-        <v>17012992</v>
+        <v>6345993</v>
       </c>
     </row>
     <row r="7">
@@ -606,25 +606,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2765</v>
+        <v>979</v>
       </c>
       <c r="E7" t="n">
-        <v>4693.7</v>
+        <v>5044.5</v>
       </c>
       <c r="F7" t="n">
-        <v>3923.4</v>
+        <v>4649.5</v>
       </c>
       <c r="G7" t="n">
-        <v>17347850</v>
+        <v>4494146</v>
       </c>
     </row>
     <row r="8">
@@ -640,49 +640,49 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4637</v>
+        <v>237</v>
       </c>
       <c r="E8" t="n">
-        <v>4484.6875</v>
+        <v>5242</v>
       </c>
       <c r="F8" t="n">
-        <v>3776.4375</v>
+        <v>4582.5</v>
       </c>
       <c r="G8" t="n">
-        <v>22034450</v>
+        <v>1264131</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3092</v>
+        <v>1216</v>
       </c>
       <c r="E9" t="n">
-        <v>3342</v>
+        <v>5585</v>
       </c>
       <c r="F9" t="n">
-        <v>2732.041666666667</v>
+        <v>4953</v>
       </c>
       <c r="G9" t="n">
-        <v>9754144</v>
+        <v>7011796</v>
       </c>
     </row>
     <row r="10">
@@ -693,7 +693,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -702,16 +702,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2342</v>
+        <v>460</v>
       </c>
       <c r="E10" t="n">
-        <v>5254.4</v>
+        <v>3438</v>
       </c>
       <c r="F10" t="n">
-        <v>4658.5</v>
+        <v>3070</v>
       </c>
       <c r="G10" t="n">
-        <v>11857754</v>
+        <v>1581480</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -731,27 +731,27 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1506</v>
+        <v>1397</v>
       </c>
       <c r="E11" t="n">
-        <v>5021.25</v>
+        <v>3676.25</v>
       </c>
       <c r="F11" t="n">
-        <v>4065.75</v>
+        <v>2948.25</v>
       </c>
       <c r="G11" t="n">
-        <v>5576959</v>
+        <v>5024884</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -760,22 +760,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1610</v>
+        <v>558</v>
       </c>
       <c r="E12" t="n">
-        <v>4709.8</v>
+        <v>3274</v>
       </c>
       <c r="F12" t="n">
-        <v>3963.1</v>
+        <v>2855</v>
       </c>
       <c r="G12" t="n">
-        <v>8473693</v>
+        <v>1826892</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -785,20 +785,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3152</v>
+        <v>201</v>
       </c>
       <c r="E13" t="n">
-        <v>3866.357142857143</v>
+        <v>6716</v>
       </c>
       <c r="F13" t="n">
-        <v>3272.5</v>
+        <v>4996</v>
       </c>
       <c r="G13" t="n">
-        <v>12779231</v>
+        <v>1349916</v>
       </c>
     </row>
     <row r="14">
@@ -809,31 +809,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2571</v>
+        <v>67</v>
       </c>
       <c r="E14" t="n">
-        <v>3100.5</v>
+        <v>5351</v>
       </c>
       <c r="F14" t="n">
-        <v>2780.5</v>
+        <v>4776</v>
       </c>
       <c r="G14" t="n">
-        <v>8053811</v>
+        <v>358517</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -843,26 +843,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1153</v>
+        <v>1794</v>
       </c>
       <c r="E15" t="n">
-        <v>1956.5</v>
+        <v>3664.25</v>
       </c>
       <c r="F15" t="n">
-        <v>1771</v>
+        <v>3506.25</v>
       </c>
       <c r="G15" t="n">
-        <v>2208814</v>
+        <v>4592101</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3378</v>
+        <v>224</v>
       </c>
       <c r="E16" t="n">
-        <v>4212.25</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="n">
-        <v>3645.25</v>
+        <v>3027</v>
       </c>
       <c r="G16" t="n">
-        <v>14143216</v>
+        <v>822976</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -905,22 +905,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4513</v>
+        <v>1164</v>
       </c>
       <c r="E17" t="n">
-        <v>5089.738095238095</v>
+        <v>3336.666666666667</v>
       </c>
       <c r="F17" t="n">
-        <v>4458.952380952381</v>
+        <v>2944</v>
       </c>
       <c r="G17" t="n">
-        <v>20507621</v>
+        <v>2578735</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -934,22 +934,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4694</v>
+        <v>115</v>
       </c>
       <c r="E18" t="n">
-        <v>4410.571428571428</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="n">
-        <v>3860.904761904762</v>
+        <v>4697</v>
       </c>
       <c r="G18" t="n">
-        <v>16668146</v>
+        <v>746005</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -963,22 +963,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2585</v>
+        <v>193</v>
       </c>
       <c r="E19" t="n">
-        <v>2711.75</v>
+        <v>6360</v>
       </c>
       <c r="F19" t="n">
-        <v>2441.125</v>
+        <v>6356</v>
       </c>
       <c r="G19" t="n">
-        <v>6740303</v>
+        <v>1227480</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -988,55 +988,55 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>871</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>4727</v>
+        <v>2244</v>
       </c>
       <c r="F20" t="n">
-        <v>4162.833333333333</v>
+        <v>2172</v>
       </c>
       <c r="G20" t="n">
-        <v>3725895</v>
+        <v>22440</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>27110</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5836</v>
+        <v>396</v>
       </c>
       <c r="E21" t="n">
-        <v>4102.722222222223</v>
+        <v>2933</v>
       </c>
       <c r="F21" t="n">
-        <v>3601.814814814815</v>
+        <v>2389</v>
       </c>
       <c r="G21" t="n">
-        <v>21914642</v>
+        <v>1161468</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>27110</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1046,31 +1046,31 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2984</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4308.75</v>
+        <v>7710</v>
       </c>
       <c r="F22" t="n">
-        <v>3589.75</v>
+        <v>7600</v>
       </c>
       <c r="G22" t="n">
-        <v>12063968</v>
+        <v>61680</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>27110</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1079,27 +1079,27 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2106</v>
+        <v>166</v>
       </c>
       <c r="E23" t="n">
-        <v>5337</v>
+        <v>7863</v>
       </c>
       <c r="F23" t="n">
-        <v>4478.5</v>
+        <v>7837</v>
       </c>
       <c r="G23" t="n">
-        <v>10530629</v>
+        <v>1305258</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>28110</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1108,27 +1108,27 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3920</v>
+        <v>194</v>
       </c>
       <c r="E24" t="n">
-        <v>4988.625</v>
+        <v>4162</v>
       </c>
       <c r="F24" t="n">
-        <v>4118.875</v>
+        <v>4117</v>
       </c>
       <c r="G24" t="n">
-        <v>18929014</v>
+        <v>807428</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>28110</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1137,22 +1137,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2585</v>
+        <v>713</v>
       </c>
       <c r="E25" t="n">
-        <v>4361.9</v>
+        <v>6877</v>
       </c>
       <c r="F25" t="n">
-        <v>3506.2</v>
+        <v>6853</v>
       </c>
       <c r="G25" t="n">
-        <v>13119098</v>
+        <v>4903301</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>41110</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1166,22 +1166,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4743</v>
+        <v>325</v>
       </c>
       <c r="E26" t="n">
-        <v>3410.633333333333</v>
+        <v>6899</v>
       </c>
       <c r="F26" t="n">
-        <v>2862.433333333333</v>
+        <v>5405</v>
       </c>
       <c r="G26" t="n">
-        <v>13610811</v>
+        <v>2242175</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>41110</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1195,22 +1195,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1944</v>
+        <v>1522</v>
       </c>
       <c r="E27" t="n">
-        <v>5731</v>
+        <v>5438</v>
       </c>
       <c r="F27" t="n">
-        <v>5185.25</v>
+        <v>4718.75</v>
       </c>
       <c r="G27" t="n">
-        <v>10178358</v>
+        <v>8746693</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>41110</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1224,22 +1224,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1178</v>
+        <v>1833</v>
       </c>
       <c r="E28" t="n">
-        <v>5962.25</v>
+        <v>4210.333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>5090</v>
+        <v>3673.166666666667</v>
       </c>
       <c r="G28" t="n">
-        <v>7637378</v>
+        <v>7060095</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>41110</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1253,51 +1253,51 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2627</v>
+        <v>1146</v>
       </c>
       <c r="E29" t="n">
-        <v>4683.625</v>
+        <v>5909.5</v>
       </c>
       <c r="F29" t="n">
-        <v>4302.25</v>
+        <v>4736.5</v>
       </c>
       <c r="G29" t="n">
-        <v>10212285</v>
+        <v>6939153</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3674</v>
+        <v>259</v>
       </c>
       <c r="E30" t="n">
-        <v>4606.833333333334</v>
+        <v>2605</v>
       </c>
       <c r="F30" t="n">
-        <v>4003.466666666666</v>
+        <v>2220</v>
       </c>
       <c r="G30" t="n">
-        <v>17132174</v>
+        <v>674695</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>41150</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1307,26 +1307,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3540</v>
+        <v>686</v>
       </c>
       <c r="E31" t="n">
-        <v>4156.2</v>
+        <v>4491</v>
       </c>
       <c r="F31" t="n">
-        <v>3766.1</v>
+        <v>3847</v>
       </c>
       <c r="G31" t="n">
-        <v>14856773</v>
+        <v>3080826</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>41150</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1340,22 +1340,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2637</v>
+        <v>1030</v>
       </c>
       <c r="E32" t="n">
-        <v>5614.5</v>
+        <v>5412.75</v>
       </c>
       <c r="F32" t="n">
-        <v>4423</v>
+        <v>4495.25</v>
       </c>
       <c r="G32" t="n">
-        <v>15369444</v>
+        <v>4729098</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>41150</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1369,22 +1369,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1097</v>
+        <v>657</v>
       </c>
       <c r="E33" t="n">
-        <v>2936</v>
+        <v>5978</v>
       </c>
       <c r="F33" t="n">
-        <v>2526</v>
+        <v>4592.5</v>
       </c>
       <c r="G33" t="n">
-        <v>4455704</v>
+        <v>3048321</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>42110</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1398,51 +1398,51 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>448</v>
+        <v>331</v>
       </c>
       <c r="E34" t="n">
-        <v>6561.666666666667</v>
+        <v>7595</v>
       </c>
       <c r="F34" t="n">
-        <v>5354.333333333333</v>
+        <v>7046</v>
       </c>
       <c r="G34" t="n">
-        <v>3137712</v>
+        <v>2513945</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>42110</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2848</v>
+        <v>272</v>
       </c>
       <c r="E35" t="n">
-        <v>3489.8</v>
+        <v>2615.5</v>
       </c>
       <c r="F35" t="n">
-        <v>2930.2</v>
+        <v>2309.5</v>
       </c>
       <c r="G35" t="n">
-        <v>12531297</v>
+        <v>623636</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>42110</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1452,55 +1452,55 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3508</v>
+        <v>199</v>
       </c>
       <c r="E36" t="n">
-        <v>4347.125</v>
+        <v>3243</v>
       </c>
       <c r="F36" t="n">
-        <v>3795.541666666667</v>
+        <v>2918</v>
       </c>
       <c r="G36" t="n">
-        <v>13140555</v>
+        <v>645357</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1322</v>
+        <v>234</v>
       </c>
       <c r="E37" t="n">
-        <v>5139.75</v>
+        <v>6633</v>
       </c>
       <c r="F37" t="n">
-        <v>4393.5</v>
+        <v>4955</v>
       </c>
       <c r="G37" t="n">
-        <v>7472065</v>
+        <v>1552122</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1510,55 +1510,55 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1552</v>
+        <v>366</v>
       </c>
       <c r="E38" t="n">
-        <v>6521.166666666667</v>
+        <v>5645.5</v>
       </c>
       <c r="F38" t="n">
-        <v>5072.666666666667</v>
+        <v>4981</v>
       </c>
       <c r="G38" t="n">
-        <v>7856155</v>
+        <v>2191500</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2326</v>
+        <v>790</v>
       </c>
       <c r="E39" t="n">
-        <v>4772.642857142857</v>
+        <v>4964</v>
       </c>
       <c r="F39" t="n">
-        <v>4136.5</v>
+        <v>4138</v>
       </c>
       <c r="G39" t="n">
-        <v>11481872</v>
+        <v>3626524</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1568,60 +1568,60 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4598</v>
+        <v>676</v>
       </c>
       <c r="E40" t="n">
-        <v>3225.047619047619</v>
+        <v>7893</v>
       </c>
       <c r="F40" t="n">
-        <v>2674.142857142857</v>
+        <v>5749</v>
       </c>
       <c r="G40" t="n">
-        <v>16540054</v>
+        <v>5335668</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D41" t="n">
+        <v>663</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3496</v>
+      </c>
+      <c r="F41" t="n">
         <v>3456</v>
       </c>
-      <c r="E41" t="n">
-        <v>3716.533333333334</v>
-      </c>
-      <c r="F41" t="n">
-        <v>3281.6</v>
-      </c>
       <c r="G41" t="n">
-        <v>13484629</v>
+        <v>2317848</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>41150</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1630,22 +1630,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3168</v>
+        <v>324</v>
       </c>
       <c r="E42" t="n">
-        <v>4887</v>
+        <v>1730.5</v>
       </c>
       <c r="F42" t="n">
-        <v>4123.666666666667</v>
+        <v>1457.5</v>
       </c>
       <c r="G42" t="n">
-        <v>14614557</v>
+        <v>721467</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>41150</t>
+          <t>45110</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1655,55 +1655,55 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2799</v>
+        <v>633</v>
       </c>
       <c r="E43" t="n">
-        <v>5737.875</v>
+        <v>5031</v>
       </c>
       <c r="F43" t="n">
-        <v>5287.5</v>
+        <v>4209</v>
       </c>
       <c r="G43" t="n">
-        <v>14146023</v>
+        <v>3184623</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>41150</t>
+          <t>45110</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2404</v>
+        <v>15</v>
       </c>
       <c r="E44" t="n">
-        <v>3466.25</v>
+        <v>7485</v>
       </c>
       <c r="F44" t="n">
-        <v>2919.833333333333</v>
+        <v>6988</v>
       </c>
       <c r="G44" t="n">
-        <v>6728104</v>
+        <v>112275</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>41150</t>
+          <t>45110</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1713,55 +1713,55 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1906</v>
+        <v>585</v>
       </c>
       <c r="E45" t="n">
-        <v>4514.666666666667</v>
+        <v>5097</v>
       </c>
       <c r="F45" t="n">
-        <v>3803.333333333333</v>
+        <v>3804</v>
       </c>
       <c r="G45" t="n">
-        <v>7742370</v>
+        <v>2981745</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>45110</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1876</v>
+        <v>453</v>
       </c>
       <c r="E46" t="n">
-        <v>6294.333333333333</v>
+        <v>1320.5</v>
       </c>
       <c r="F46" t="n">
-        <v>5230.333333333333</v>
+        <v>1164</v>
       </c>
       <c r="G46" t="n">
-        <v>11893014</v>
+        <v>1196232</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>46110</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1771,55 +1771,55 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1614</v>
+        <v>1292</v>
       </c>
       <c r="E47" t="n">
-        <v>4239.285714285715</v>
+        <v>3849.5</v>
       </c>
       <c r="F47" t="n">
-        <v>3687</v>
+        <v>2955.5</v>
       </c>
       <c r="G47" t="n">
-        <v>8063824</v>
+        <v>5617783</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>46110</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1797</v>
+        <v>479</v>
       </c>
       <c r="E48" t="n">
-        <v>3805</v>
+        <v>3190</v>
       </c>
       <c r="F48" t="n">
-        <v>3382.3</v>
+        <v>3093</v>
       </c>
       <c r="G48" t="n">
-        <v>6674399</v>
+        <v>1528010</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>46110</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1833,27 +1833,27 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1372</v>
+        <v>218</v>
       </c>
       <c r="E49" t="n">
-        <v>5456.4</v>
+        <v>2357</v>
       </c>
       <c r="F49" t="n">
-        <v>4711.9</v>
+        <v>1821</v>
       </c>
       <c r="G49" t="n">
-        <v>8109537</v>
+        <v>492786</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1862,27 +1862,27 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3746</v>
+        <v>1588</v>
       </c>
       <c r="E50" t="n">
-        <v>4554.125</v>
+        <v>4269</v>
       </c>
       <c r="F50" t="n">
-        <v>3703</v>
+        <v>3958</v>
       </c>
       <c r="G50" t="n">
-        <v>16929421</v>
+        <v>6409188</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1891,538 +1891,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1048</v>
+        <v>743</v>
       </c>
       <c r="E51" t="n">
-        <v>5882.75</v>
+        <v>6753</v>
       </c>
       <c r="F51" t="n">
-        <v>4811.25</v>
+        <v>6497</v>
       </c>
       <c r="G51" t="n">
-        <v>6629500</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>43110</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2184</v>
-      </c>
-      <c r="E52" t="n">
-        <v>4522.583333333333</v>
-      </c>
-      <c r="F52" t="n">
-        <v>3755.25</v>
-      </c>
-      <c r="G52" t="n">
-        <v>8316131</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>43110</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>1957</v>
-      </c>
-      <c r="E53" t="n">
-        <v>5132.5</v>
-      </c>
-      <c r="F53" t="n">
-        <v>4292.5</v>
-      </c>
-      <c r="G53" t="n">
-        <v>11606995</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>44130</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>3526</v>
-      </c>
-      <c r="E54" t="n">
-        <v>5058.36111111111</v>
-      </c>
-      <c r="F54" t="n">
-        <v>3979.777777777777</v>
-      </c>
-      <c r="G54" t="n">
-        <v>16271893</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>44130</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>5385</v>
-      </c>
-      <c r="E55" t="n">
-        <v>5200.071428571428</v>
-      </c>
-      <c r="F55" t="n">
-        <v>4320.357142857143</v>
-      </c>
-      <c r="G55" t="n">
-        <v>28051310</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>44130</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>3580</v>
-      </c>
-      <c r="E56" t="n">
-        <v>4204.25</v>
-      </c>
-      <c r="F56" t="n">
-        <v>3597.527777777778</v>
-      </c>
-      <c r="G56" t="n">
-        <v>19265897</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>44130</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>1645</v>
-      </c>
-      <c r="E57" t="n">
-        <v>6289.5</v>
-      </c>
-      <c r="F57" t="n">
-        <v>5435.25</v>
-      </c>
-      <c r="G57" t="n">
-        <v>9872719</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>45110</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>5619</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2643.958333333333</v>
-      </c>
-      <c r="F58" t="n">
-        <v>2236.333333333333</v>
-      </c>
-      <c r="G58" t="n">
-        <v>15556719</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>45110</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>3749</v>
-      </c>
-      <c r="E59" t="n">
-        <v>5704.809523809524</v>
-      </c>
-      <c r="F59" t="n">
-        <v>5189.809523809524</v>
-      </c>
-      <c r="G59" t="n">
-        <v>21488017</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>45110</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>2642</v>
-      </c>
-      <c r="E60" t="n">
-        <v>3852.166666666667</v>
-      </c>
-      <c r="F60" t="n">
-        <v>3134.5</v>
-      </c>
-      <c r="G60" t="n">
-        <v>9465763</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>45110</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2010</v>
-      </c>
-      <c r="E61" t="n">
-        <v>4426.5</v>
-      </c>
-      <c r="F61" t="n">
-        <v>3732.4</v>
-      </c>
-      <c r="G61" t="n">
-        <v>11469261</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>46110</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>5109</v>
-      </c>
-      <c r="E62" t="n">
-        <v>3594.142857142857</v>
-      </c>
-      <c r="F62" t="n">
-        <v>3022.714285714286</v>
-      </c>
-      <c r="G62" t="n">
-        <v>21480780</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>46110</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1412</v>
-      </c>
-      <c r="E63" t="n">
-        <v>3788.333333333333</v>
-      </c>
-      <c r="F63" t="n">
-        <v>3434.333333333333</v>
-      </c>
-      <c r="G63" t="n">
-        <v>6134978</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>46110</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>1475</v>
-      </c>
-      <c r="E64" t="n">
-        <v>3918</v>
-      </c>
-      <c r="F64" t="n">
-        <v>3301.666666666667</v>
-      </c>
-      <c r="G64" t="n">
-        <v>6614074</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>46110</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>2812</v>
-      </c>
-      <c r="E65" t="n">
-        <v>3685.666666666667</v>
-      </c>
-      <c r="F65" t="n">
-        <v>3204.458333333333</v>
-      </c>
-      <c r="G65" t="n">
-        <v>13749808</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>47110</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>3572</v>
-      </c>
-      <c r="E66" t="n">
-        <v>2947</v>
-      </c>
-      <c r="F66" t="n">
-        <v>2521.75</v>
-      </c>
-      <c r="G66" t="n">
-        <v>11179614</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>47110</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>1968</v>
-      </c>
-      <c r="E67" t="n">
-        <v>5784.5</v>
-      </c>
-      <c r="F67" t="n">
-        <v>5257.25</v>
-      </c>
-      <c r="G67" t="n">
-        <v>10617686</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>47110</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>4149</v>
-      </c>
-      <c r="E68" t="n">
-        <v>5573.3125</v>
-      </c>
-      <c r="F68" t="n">
-        <v>4872.125</v>
-      </c>
-      <c r="G68" t="n">
-        <v>20896657</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>47110</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>3582</v>
-      </c>
-      <c r="E69" t="n">
-        <v>4602.611111111111</v>
-      </c>
-      <c r="F69" t="n">
-        <v>4058</v>
-      </c>
-      <c r="G69" t="n">
-        <v>15639097</v>
+        <v>5017479</v>
       </c>
     </row>
   </sheetData>
